--- a/docs/import-templates/customer-master-template.xlsx
+++ b/docs/import-templates/customer-master-template.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="98">
   <si>
     <t>cust_code</t>
   </si>
@@ -56,6 +56,15 @@
     <t>temix_code</t>
   </si>
   <si>
+    <t>channel</t>
+  </si>
+  <si>
+    <t>day_of_visit</t>
+  </si>
+  <si>
+    <t>customer_status</t>
+  </si>
+  <si>
     <t>C-10001</t>
   </si>
   <si>
@@ -92,6 +101,15 @@
     <t/>
   </si>
   <si>
+    <t>GENERAL_TRADE</t>
+  </si>
+  <si>
+    <t>MON</t>
+  </si>
+  <si>
+    <t>ACTIVE</t>
+  </si>
+  <si>
     <t>02</t>
   </si>
   <si>
@@ -104,6 +122,9 @@
     <t>Seeb Souq, Muscat</t>
   </si>
   <si>
+    <t>WED</t>
+  </si>
+  <si>
     <t>C-10002</t>
   </si>
   <si>
@@ -143,6 +164,12 @@
     <t>TMX-10002</t>
   </si>
   <si>
+    <t>HORECA</t>
+  </si>
+  <si>
+    <t>SUN</t>
+  </si>
+  <si>
     <t>NMWC — CUSTOMER MASTER import</t>
   </si>
   <si>
@@ -255,6 +282,24 @@
   </si>
   <si>
     <t>Fill for customers already in Temix (links CRM ↔ Temix). Leave blank if not yet in Temix.</t>
+  </si>
+  <si>
+    <t>HORECA, MODERN_TRADE, GENERAL_TRADE, CONVENIENCE_AND_GAS, ECOMMERCE, HOME_OFFICE_DELIVERY, INSTITUTIONS</t>
+  </si>
+  <si>
+    <t>The CRM channel CODE. Anything else → row held for review. Blank = not set (the salesman fills it in later).</t>
+  </si>
+  <si>
+    <t>SAT, SUN, MON, TUE, WED, THU or FRI</t>
+  </si>
+  <si>
+    <t>The journey-plan visit day for this branch. Drives the salesman's Today list. Anything else → row held for review.</t>
+  </si>
+  <si>
+    <t>ACTIVE or CLOSED (default ACTIVE)</t>
+  </si>
+  <si>
+    <t>CLOSED marks the branch (and, if every branch is closed, the customer) as closed on load. A customer with any ACTIVE branch stays ACTIVE.</t>
   </si>
   <si>
     <t>⚠ REGION &amp; ROUTE ARE CODES: "sales_region" holds a region CODE (e.g. MCT) and "route" holds a route CODE (e.g. MCT-01) — the exact codes from your Account master, not display names. If your source file has names, translate them to codes first, or the rows fall back to UNASSIGNED.</t>
@@ -680,7 +725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
@@ -692,10 +737,12 @@
     <col min="11" max="11" width="17" customWidth="1"/>
     <col min="12" max="12" width="16" customWidth="1"/>
     <col min="13" max="13" width="21" customWidth="1"/>
-    <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="14" max="15" width="14" customWidth="1"/>
+    <col min="16" max="16" width="16" customWidth="1"/>
+    <col min="17" max="17" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="20" customHeight="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -738,137 +785,173 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="C3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q4" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -879,7 +962,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -890,156 +973,156 @@
   <sheetData>
     <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1047,13 +1130,13 @@
         <v>0</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1061,13 +1144,13 @@
         <v>1</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1075,13 +1158,13 @@
         <v>2</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1089,13 +1172,13 @@
         <v>3</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1103,13 +1186,13 @@
         <v>4</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1117,13 +1200,13 @@
         <v>5</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1131,13 +1214,13 @@
         <v>6</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1145,13 +1228,13 @@
         <v>7</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1159,13 +1242,13 @@
         <v>8</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1173,13 +1256,13 @@
         <v>9</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1187,13 +1270,13 @@
         <v>10</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1201,13 +1284,13 @@
         <v>11</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1215,13 +1298,13 @@
         <v>12</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1229,55 +1312,97 @@
         <v>13</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>25</v>
+        <v>92</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>25</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>25</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
